--- a/Excel/Vertical/perbandingan_Panjang Jalur.xlsx
+++ b/Excel/Vertical/perbandingan_Panjang Jalur.xlsx
@@ -542,10 +542,10 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6">
-        <v>0.6363636363636364</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="G6" t="s">
         <v>12</v>
@@ -565,10 +565,10 @@
         <v>8</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7">
-        <v>0.7954545454545454</v>
+        <v>0.75</v>
       </c>
       <c r="G7" t="s">
         <v>12</v>
@@ -588,10 +588,10 @@
         <v>8</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F8">
-        <v>0.8977272727272727</v>
+        <v>0.875</v>
       </c>
       <c r="G8" t="s">
         <v>12</v>
@@ -611,10 +611,10 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F9">
-        <v>0.9431818181818182</v>
+        <v>0.9375</v>
       </c>
       <c r="G9" t="s">
         <v>12</v>
@@ -680,10 +680,10 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>0.8369565217391305</v>
+        <v>0.8152173913043478</v>
       </c>
       <c r="G12" t="s">
         <v>12</v>
@@ -703,10 +703,10 @@
         <v>9</v>
       </c>
       <c r="E13">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F13">
-        <v>0.9184782608695652</v>
+        <v>0.9076086956521739</v>
       </c>
       <c r="G13" t="s">
         <v>12</v>
@@ -726,10 +726,10 @@
         <v>10</v>
       </c>
       <c r="E14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="G14" t="s">
         <v>12</v>
@@ -795,10 +795,10 @@
         <v>10</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17">
-        <v>0.9375</v>
+        <v>0.95</v>
       </c>
       <c r="G17" t="s">
         <v>12</v>
@@ -841,10 +841,10 @@
         <v>11</v>
       </c>
       <c r="E19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F19">
-        <v>0.8421052631578947</v>
+        <v>0.868421052631579</v>
       </c>
       <c r="G19" t="s">
         <v>12</v>
@@ -864,10 +864,10 @@
         <v>11</v>
       </c>
       <c r="E20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>0.9210526315789473</v>
+        <v>0.9342105263157895</v>
       </c>
       <c r="G20" t="s">
         <v>12</v>
@@ -887,10 +887,10 @@
         <v>11</v>
       </c>
       <c r="E21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21">
-        <v>0.9605263157894737</v>
+        <v>0.9671052631578947</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>

--- a/Excel/Vertical/perbandingan_Panjang Jalur.xlsx
+++ b/Excel/Vertical/perbandingan_Panjang Jalur.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="14">
   <si>
     <t>Kombinasi</t>
   </si>
@@ -22,7 +22,7 @@
     <t>Ukuran</t>
   </si>
   <si>
-    <t>Nilai</t>
+    <t>value</t>
   </si>
   <si>
     <t>Map</t>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>Tetap</t>
+  </si>
+  <si>
+    <t>Naik</t>
   </si>
 </sst>
 </file>
@@ -449,6 +452,12 @@
       <c r="D2" t="s">
         <v>3</v>
       </c>
+      <c r="E2">
+        <v>21</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
@@ -466,6 +475,12 @@
       <c r="D3" t="s">
         <v>3</v>
       </c>
+      <c r="E3">
+        <v>42</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
       <c r="G3" t="s">
         <v>12</v>
       </c>
@@ -483,6 +498,12 @@
       <c r="D4" t="s">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>84</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
       <c r="G4" t="s">
         <v>12</v>
       </c>
@@ -500,6 +521,12 @@
       <c r="D5" t="s">
         <v>3</v>
       </c>
+      <c r="E5">
+        <v>168</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
       <c r="G5" t="s">
         <v>12</v>
       </c>
@@ -517,8 +544,14 @@
       <c r="D6" t="s">
         <v>8</v>
       </c>
+      <c r="E6">
+        <v>21</v>
+      </c>
+      <c r="F6">
+        <v>0.04545454545454546</v>
+      </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -534,8 +567,14 @@
       <c r="D7" t="s">
         <v>8</v>
       </c>
+      <c r="E7">
+        <v>42</v>
+      </c>
+      <c r="F7">
+        <v>0.04545454545454546</v>
+      </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -551,8 +590,14 @@
       <c r="D8" t="s">
         <v>8</v>
       </c>
+      <c r="E8">
+        <v>84</v>
+      </c>
+      <c r="F8">
+        <v>0.04545454545454546</v>
+      </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -568,8 +613,14 @@
       <c r="D9" t="s">
         <v>8</v>
       </c>
+      <c r="E9">
+        <v>168</v>
+      </c>
+      <c r="F9">
+        <v>0.04545454545454546</v>
+      </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -585,8 +636,14 @@
       <c r="D10" t="s">
         <v>9</v>
       </c>
+      <c r="E10">
+        <v>21</v>
+      </c>
+      <c r="F10">
+        <v>0.08695652173913043</v>
+      </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -602,8 +659,14 @@
       <c r="D11" t="s">
         <v>9</v>
       </c>
+      <c r="E11">
+        <v>42</v>
+      </c>
+      <c r="F11">
+        <v>0.08695652173913043</v>
+      </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -619,8 +682,14 @@
       <c r="D12" t="s">
         <v>9</v>
       </c>
+      <c r="E12">
+        <v>84</v>
+      </c>
+      <c r="F12">
+        <v>0.08695652173913043</v>
+      </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -636,8 +705,14 @@
       <c r="D13" t="s">
         <v>9</v>
       </c>
+      <c r="E13">
+        <v>168</v>
+      </c>
+      <c r="F13">
+        <v>0.08695652173913043</v>
+      </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -653,8 +728,14 @@
       <c r="D14" t="s">
         <v>10</v>
       </c>
+      <c r="E14">
+        <v>16</v>
+      </c>
+      <c r="F14">
+        <v>0.2</v>
+      </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -670,8 +751,14 @@
       <c r="D15" t="s">
         <v>10</v>
       </c>
+      <c r="E15">
+        <v>17</v>
+      </c>
+      <c r="F15">
+        <v>0.575</v>
+      </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -687,8 +774,14 @@
       <c r="D16" t="s">
         <v>10</v>
       </c>
+      <c r="E16">
+        <v>17</v>
+      </c>
+      <c r="F16">
+        <v>0.7875</v>
+      </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -704,8 +797,14 @@
       <c r="D17" t="s">
         <v>10</v>
       </c>
+      <c r="E17">
+        <v>17</v>
+      </c>
+      <c r="F17">
+        <v>0.89375</v>
+      </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -721,8 +820,14 @@
       <c r="D18" t="s">
         <v>11</v>
       </c>
+      <c r="E18">
+        <v>6</v>
+      </c>
+      <c r="F18">
+        <v>0.6842105263157895</v>
+      </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -738,8 +843,14 @@
       <c r="D19" t="s">
         <v>11</v>
       </c>
+      <c r="E19">
+        <v>6</v>
+      </c>
+      <c r="F19">
+        <v>0.8421052631578947</v>
+      </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -755,8 +866,14 @@
       <c r="D20" t="s">
         <v>11</v>
       </c>
+      <c r="E20">
+        <v>7</v>
+      </c>
+      <c r="F20">
+        <v>0.9078947368421053</v>
+      </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -772,8 +889,14 @@
       <c r="D21" t="s">
         <v>11</v>
       </c>
+      <c r="E21">
+        <v>7</v>
+      </c>
+      <c r="F21">
+        <v>0.9539473684210527</v>
+      </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Vertical/perbandingan_Panjang Jalur.xlsx
+++ b/Excel/Vertical/perbandingan_Panjang Jalur.xlsx
@@ -821,10 +821,10 @@
         <v>11</v>
       </c>
       <c r="E18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18">
-        <v>0.6842105263157895</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -844,10 +844,10 @@
         <v>11</v>
       </c>
       <c r="E19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19">
-        <v>0.8421052631578947</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
